--- a/data/trans_dic/P44-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,88</t>
+          <t>5,46; 9,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,45</t>
+          <t>7,91; 12,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,28; 39,41</t>
+          <t>31,69; 39,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,21</t>
+          <t>5,03; 8,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,24</t>
+          <t>6,02; 10,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,08; 29,16</t>
+          <t>24,21; 29,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,25</t>
+          <t>5,68; 8,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 10,49</t>
+          <t>7,31; 10,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,59; 32,24</t>
+          <t>27,7; 32,04</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 14,97</t>
+          <t>8,42; 15,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 14,49</t>
+          <t>9,39; 14,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,41; 76,99</t>
+          <t>33,5; 75,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 11,51</t>
+          <t>5,15; 11,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,77</t>
+          <t>3,87; 7,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 31,08</t>
+          <t>13,34; 31,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,15</t>
+          <t>7,48; 12,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,42</t>
+          <t>7,17; 10,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,38; 59,46</t>
+          <t>26,06; 59,18</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 24,1</t>
+          <t>8,43; 24,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,31; 25,29</t>
+          <t>11,83; 25,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,89; 51,23</t>
+          <t>38,93; 50,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 31,84</t>
+          <t>11,39; 33,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 22,23</t>
+          <t>7,43; 20,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,1; 43,43</t>
+          <t>34,13; 43,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 23,67</t>
+          <t>11,19; 24,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 20,62</t>
+          <t>11,44; 20,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,7; 46,07</t>
+          <t>38,2; 45,91</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 11,46</t>
+          <t>7,92; 11,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,58</t>
+          <t>10,17; 13,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,89; 66,42</t>
+          <t>35,68; 64,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,0</t>
+          <t>6,1; 8,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,87</t>
+          <t>6,15; 8,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,0; 30,64</t>
+          <t>17,57; 30,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,55</t>
+          <t>7,25; 9,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,55</t>
+          <t>8,42; 10,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,31; 49,53</t>
+          <t>29,09; 48,8</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35779; 64250</t>
+          <t>35533; 64050</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42432; 68451</t>
+          <t>43484; 69668</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126013; 158738</t>
+          <t>127653; 158508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51003; 83092</t>
+          <t>50968; 83152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50018; 83122</t>
+          <t>48855; 82998</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>154090; 186636</t>
+          <t>154958; 188908</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93432; 137207</t>
+          <t>94473; 137127</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100172; 142838</t>
+          <t>99574; 142055</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287718; 336191</t>
+          <t>288871; 334072</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36013; 65349</t>
+          <t>36764; 67877</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63310; 98864</t>
+          <t>64060; 98870</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>342689; 789756</t>
+          <t>343676; 778037</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20162; 44785</t>
+          <t>20039; 43475</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26328; 51135</t>
+          <t>25486; 51976</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121810; 292207</t>
+          <t>125442; 291936</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61940; 100330</t>
+          <t>61766; 100043</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>98114; 139668</t>
+          <t>96142; 137895</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>498957; 1168903</t>
+          <t>512364; 1163381</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8614; 25290</t>
+          <t>8847; 25258</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19996; 41071</t>
+          <t>19219; 40786</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107994; 142239</t>
+          <t>108093; 139115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6570; 20057</t>
+          <t>7177; 21011</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9665; 27053</t>
+          <t>9038; 25180</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75463; 96112</t>
+          <t>75517; 96720</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18591; 39744</t>
+          <t>18793; 40651</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32853; 58574</t>
+          <t>32506; 59625</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>188094; 229858</t>
+          <t>190620; 229056</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92904; 136614</t>
+          <t>94338; 137296</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141606; 189442</t>
+          <t>141796; 192300</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>612371; 1133268</t>
+          <t>608739; 1098584</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88445; 131781</t>
+          <t>89318; 131620</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>98246; 141118</t>
+          <t>97926; 142018</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>324322; 551922</t>
+          <t>316452; 550079</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>193727; 253523</t>
+          <t>192644; 253366</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>249669; 315051</t>
+          <t>251348; 314389</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1028084; 1737384</t>
+          <t>1020576; 1711635</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,85</t>
+          <t>5,48; 10,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,91; 12,68</t>
+          <t>7,77; 12,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,69; 39,35</t>
+          <t>31,05; 38,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,21</t>
+          <t>5,13; 8,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,23</t>
+          <t>6,21; 10,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,21; 29,52</t>
+          <t>24,88; 29,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,25</t>
+          <t>5,58; 8,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,44</t>
+          <t>7,22; 10,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,7; 32,04</t>
+          <t>28,03; 32,28</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 15,55</t>
+          <t>8,47; 15,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,49</t>
+          <t>9,57; 14,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,5; 75,84</t>
+          <t>31,1; 36,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,17</t>
+          <t>5,39; 11,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,9</t>
+          <t>4,08; 7,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 31,05</t>
+          <t>27,99; 32,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 12,12</t>
+          <t>7,58; 12,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 10,29</t>
+          <t>7,28; 10,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 59,18</t>
+          <t>30,27; 34,1</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 24,07</t>
+          <t>7,82; 23,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 25,11</t>
+          <t>12,12; 25,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,93; 50,1</t>
+          <t>38,39; 49,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 33,36</t>
+          <t>10,84; 33,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 20,69</t>
+          <t>7,67; 21,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,13; 43,71</t>
+          <t>33,63; 43,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 24,21</t>
+          <t>10,86; 23,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,44; 20,99</t>
+          <t>11,49; 21,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,2; 45,91</t>
+          <t>38,14; 45,24</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 11,52</t>
+          <t>7,66; 11,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,17; 13,79</t>
+          <t>10,05; 13,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,68; 64,38</t>
+          <t>33,54; 38,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,99</t>
+          <t>6,05; 8,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,93</t>
+          <t>6,13; 9,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,57; 30,54</t>
+          <t>28,71; 31,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,54</t>
+          <t>7,22; 9,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 10,53</t>
+          <t>8,38; 10,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,09; 48,8</t>
+          <t>31,62; 34,36</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142282</t>
+          <t>151674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>170682</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>312964</t>
+          <t>339742</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35533; 64050</t>
+          <t>35657; 66033</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43484; 69668</t>
+          <t>42682; 70414</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127653; 158508</t>
+          <t>135018; 169168</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50968; 83152</t>
+          <t>51978; 84553</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48855; 82998</t>
+          <t>50389; 82563</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>154958; 188908</t>
+          <t>172000; 204589</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94473; 137127</t>
+          <t>92776; 136559</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99574; 142055</t>
+          <t>98322; 142642</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>288871; 334072</t>
+          <t>315675; 363499</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>512398</t>
+          <t>291623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>223015</t>
+          <t>244815</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>735413</t>
+          <t>536437</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36764; 67877</t>
+          <t>36993; 65470</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64060; 98870</t>
+          <t>65306; 98786</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>343676; 778037</t>
+          <t>266920; 317145</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20039; 43475</t>
+          <t>20981; 44717</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25486; 51976</t>
+          <t>26872; 51890</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>125442; 291936</t>
+          <t>225950; 265687</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61766; 100043</t>
+          <t>62607; 99217</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96142; 137895</t>
+          <t>97593; 139317</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512364; 1163381</t>
+          <t>504191; 567902</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123905</t>
+          <t>130103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>209632</t>
+          <t>227223</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8847; 25258</t>
+          <t>8200; 24875</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19219; 40786</t>
+          <t>19682; 40699</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108093; 139115</t>
+          <t>113685; 145704</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7177; 21011</t>
+          <t>6828; 20868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9038; 25180</t>
+          <t>9339; 26673</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75517; 96720</t>
+          <t>83422; 108275</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18793; 40651</t>
+          <t>18232; 39440</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32506; 59625</t>
+          <t>32658; 60063</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>190620; 229056</t>
+          <t>207558; 246204</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>778586</t>
+          <t>573400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1258010</t>
+          <t>1103402</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94338; 137296</t>
+          <t>91257; 137073</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141796; 192300</t>
+          <t>140187; 192560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>608739; 1098584</t>
+          <t>532966; 604194</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89318; 131620</t>
+          <t>88565; 129757</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>97926; 142018</t>
+          <t>97510; 143518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>316452; 550079</t>
+          <t>501477; 558440</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>192644; 253366</t>
+          <t>191766; 251543</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>251348; 314389</t>
+          <t>250355; 318093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1020576; 1711635</t>
+          <t>1054982; 1146162</t>
         </is>
       </c>
     </row>
